--- a/data/trans_orig/P34A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2007</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2007 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104950</t>
+          <t>104374</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145063</t>
+          <t>142640</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>175363</t>
+          <t>175419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216381</t>
+          <t>215828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>290699</t>
+          <t>289971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>347765</t>
+          <t>349226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>342656</t>
+          <t>345079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382769</t>
+          <t>383345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241678</t>
+          <t>242231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282696</t>
+          <t>282640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598013</t>
+          <t>596552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655079</t>
+          <t>655807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236506</t>
+          <t>235396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>288727</t>
+          <t>287438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>249320</t>
+          <t>251204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>299388</t>
+          <t>302986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>503185</t>
+          <t>500842</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>573780</t>
+          <t>574341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431832</t>
+          <t>433121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484053</t>
+          <t>485163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315914</t>
+          <t>312316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365982</t>
+          <t>364098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>762080</t>
+          <t>761519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>832675</t>
+          <t>835018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>254713</t>
+          <t>256920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305643</t>
+          <t>304952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>275442</t>
+          <t>277355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>327845</t>
+          <t>327870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>544783</t>
+          <t>546626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>617290</t>
+          <t>617582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>325995</t>
+          <t>326686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>376925</t>
+          <t>374718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>347097</t>
+          <t>347072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>399500</t>
+          <t>397587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>689290</t>
+          <t>688998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>761797</t>
+          <t>759954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>231883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277212</t>
+          <t>279050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>199446</t>
+          <t>200735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>244384</t>
+          <t>243793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>444157</t>
+          <t>444107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>508028</t>
+          <t>507711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237490</t>
+          <t>235652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>284567</t>
+          <t>282819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259700</t>
+          <t>260291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304638</t>
+          <t>303349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>510758</t>
+          <t>511075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574629</t>
+          <t>574679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172075</t>
+          <t>174223</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>210685</t>
+          <t>210998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154892</t>
+          <t>155465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197777</t>
+          <t>195403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338404</t>
+          <t>340476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392394</t>
+          <t>395044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168303</t>
+          <t>167990</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206913</t>
+          <t>204765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202025</t>
+          <t>204399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>244910</t>
+          <t>244337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386396</t>
+          <t>383746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>440386</t>
+          <t>438314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96241</t>
+          <t>96667</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129155</t>
+          <t>129064</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145858</t>
+          <t>144812</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179135</t>
+          <t>179080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>251860</t>
+          <t>251636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>300168</t>
+          <t>300880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159955</t>
+          <t>160046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192869</t>
+          <t>192443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159413</t>
+          <t>159468</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>192690</t>
+          <t>193736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>327490</t>
+          <t>326778</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>375798</t>
+          <t>376022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89265</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117653</t>
+          <t>117449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>179581</t>
+          <t>180677</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216949</t>
+          <t>217114</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>279603</t>
+          <t>278446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>327889</t>
+          <t>326995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91196</t>
+          <t>91400</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119584</t>
+          <t>121460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111073</t>
+          <t>110908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148441</t>
+          <t>147345</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208981</t>
+          <t>209875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>257267</t>
+          <t>258424</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1277681</t>
+          <t>1269057</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1387470</t>
+          <t>1384498</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1471330</t>
+          <t>1475908</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1592159</t>
+          <t>1591174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2777688</t>
+          <t>2775725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2943935</t>
+          <t>2940722</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1844093</t>
+          <t>1847065</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1953882</t>
+          <t>1962506</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1726600</t>
+          <t>1727585</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1847429</t>
+          <t>1842851</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3606387</t>
+          <t>3609600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3772634</t>
+          <t>3774597</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2012</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56590</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87110</t>
+          <t>88068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107589</t>
+          <t>106636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144493</t>
+          <t>144979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171344</t>
+          <t>172624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223636</t>
+          <t>221343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>367036</t>
+          <t>366078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397556</t>
+          <t>398275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285737</t>
+          <t>285251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322641</t>
+          <t>323594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>660740</t>
+          <t>663033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713032</t>
+          <t>711752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115462</t>
+          <t>112038</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>153984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145261</t>
+          <t>147524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>193610</t>
+          <t>192243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>274145</t>
+          <t>276314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334308</t>
+          <t>333950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>531182</t>
+          <t>531345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>569867</t>
+          <t>573291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416645</t>
+          <t>418012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>464994</t>
+          <t>462731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>961277</t>
+          <t>961635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021440</t>
+          <t>1019271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,67%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148012</t>
+          <t>150448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192783</t>
+          <t>198667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176310</t>
+          <t>176983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228362</t>
+          <t>225796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>337007</t>
+          <t>337343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>402375</t>
+          <t>408844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>489080</t>
+          <t>483196</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533851</t>
+          <t>531415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>482488</t>
+          <t>485054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>534540</t>
+          <t>533867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>990337</t>
+          <t>983868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1055705</t>
+          <t>1055369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131721</t>
+          <t>130938</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>177044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151559</t>
+          <t>151874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200317</t>
+          <t>197279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>297843</t>
+          <t>296386</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>363355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>440046</t>
+          <t>437573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>482896</t>
+          <t>483679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415882</t>
+          <t>418920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464640</t>
+          <t>464325</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>863271</t>
+          <t>867461</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>932973</t>
+          <t>934430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89363</t>
+          <t>90028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127327</t>
+          <t>125968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96448</t>
+          <t>98465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135281</t>
+          <t>135731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192829</t>
+          <t>193762</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247333</t>
+          <t>250206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302102</t>
+          <t>303461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340066</t>
+          <t>339401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>312519</t>
+          <t>312069</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>351352</t>
+          <t>349335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>629896</t>
+          <t>627023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684400</t>
+          <t>683467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51609</t>
+          <t>51808</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82461</t>
+          <t>82841</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99057</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>134422</t>
+          <t>135976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>159633</t>
+          <t>159588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208467</t>
+          <t>206415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227325</t>
+          <t>226945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258177</t>
+          <t>257978</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219574</t>
+          <t>218020</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254939</t>
+          <t>254119</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455315</t>
+          <t>457367</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504149</t>
+          <t>504194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84968</t>
+          <t>85498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178138</t>
+          <t>179785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218068</t>
+          <t>219319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241869</t>
+          <t>241238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>293172</t>
+          <t>291456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164883</t>
+          <t>164353</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194646</t>
+          <t>194295</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169813</t>
+          <t>168562</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>209743</t>
+          <t>208096</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>344560</t>
+          <t>346276</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>395863</t>
+          <t>396494</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>720971</t>
+          <t>719512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>825293</t>
+          <t>820113</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1042002</t>
+          <t>1045472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1157285</t>
+          <t>1157918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1796791</t>
+          <t>1793702</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1940903</t>
+          <t>1945254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2599728</t>
+          <t>2604908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2704050</t>
+          <t>2705509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2399926</t>
+          <t>2399293</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2515209</t>
+          <t>2511739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5041329</t>
+          <t>5036978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5185441</t>
+          <t>5188530</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2016</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96455</t>
+          <t>97520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134520</t>
+          <t>133075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171488</t>
+          <t>170393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207587</t>
+          <t>205114</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258701</t>
+          <t>256251</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323008</t>
+          <t>321943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224267</t>
+          <t>225362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261235</t>
+          <t>262680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556517</t>
+          <t>558967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>607631</t>
+          <t>610104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,84%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136477</t>
+          <t>136968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180207</t>
+          <t>180016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184744</t>
+          <t>186083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229920</t>
+          <t>231965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>335393</t>
+          <t>335782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>396076</t>
+          <t>398049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410289</t>
+          <t>410480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454019</t>
+          <t>453528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333624</t>
+          <t>331579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378800</t>
+          <t>377461</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>757964</t>
+          <t>755991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818647</t>
+          <t>818258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>209648</t>
+          <t>208563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>259455</t>
+          <t>260756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204760</t>
+          <t>204566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255291</t>
+          <t>253480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>433319</t>
+          <t>429865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>501111</t>
+          <t>499539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>409642</t>
+          <t>408341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>459449</t>
+          <t>460534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>406095</t>
+          <t>407906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456626</t>
+          <t>456820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>829372</t>
+          <t>830944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>897164</t>
+          <t>900618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222635</t>
+          <t>222356</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>274902</t>
+          <t>273021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223313</t>
+          <t>221032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>274177</t>
+          <t>271466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>462981</t>
+          <t>459016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>537582</t>
+          <t>530703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371146</t>
+          <t>373027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>423413</t>
+          <t>423692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>374900</t>
+          <t>377611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>425764</t>
+          <t>428045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>757543</t>
+          <t>764422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>832144</t>
+          <t>836109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149986</t>
+          <t>150050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193788</t>
+          <t>193581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204046</t>
+          <t>204399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252033</t>
+          <t>252073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>369823</t>
+          <t>369256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434676</t>
+          <t>433293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>284130</t>
+          <t>284337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>327932</t>
+          <t>327868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244816</t>
+          <t>244776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292803</t>
+          <t>292450</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>540091</t>
+          <t>541474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>604944</t>
+          <t>605511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110487</t>
+          <t>110713</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145439</t>
+          <t>146706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>155051</t>
+          <t>153400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193497</t>
+          <t>194620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>273583</t>
+          <t>271902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>327381</t>
+          <t>327241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,95%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188891</t>
+          <t>187624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223843</t>
+          <t>223617</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184265</t>
+          <t>183142</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222711</t>
+          <t>224362</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384711</t>
+          <t>384851</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>438509</t>
+          <t>440190</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116564</t>
+          <t>118885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146526</t>
+          <t>145032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>253220</t>
+          <t>252222</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>295803</t>
+          <t>293516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>379139</t>
+          <t>378262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431035</t>
+          <t>431568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110472</t>
+          <t>111966</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>140434</t>
+          <t>138113</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104366</t>
+          <t>106653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146949</t>
+          <t>147947</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>226132</t>
+          <t>225599</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278028</t>
+          <t>278905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1091965</t>
+          <t>1093989</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1204174</t>
+          <t>1211924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1451762</t>
+          <t>1455725</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1571420</t>
+          <t>1574322</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2570329</t>
+          <t>2579108</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2735966</t>
+          <t>2745765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2190176</t>
+          <t>2182426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2302385</t>
+          <t>2300361</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1973122</t>
+          <t>1970220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2092780</t>
+          <t>2088817</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4202926</t>
+          <t>4193127</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4368563</t>
+          <t>4359784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2023</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34699</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87040</t>
+          <t>89716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95081</t>
+          <t>94030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140997</t>
+          <t>140381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140340</t>
+          <t>140568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209471</t>
+          <t>209794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312947</t>
+          <t>310271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>365288</t>
+          <t>363662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172203</t>
+          <t>172819</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>218119</t>
+          <t>219170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503716</t>
+          <t>503393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572847</t>
+          <t>572619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>127370</t>
+          <t>126601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>175965</t>
+          <t>174915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95609</t>
+          <t>98893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>200430</t>
+          <t>198489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>242689</t>
+          <t>240494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>359634</t>
+          <t>355830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>246396</t>
+          <t>247446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294991</t>
+          <t>295760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311074</t>
+          <t>313015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>415895</t>
+          <t>412611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>574231</t>
+          <t>578035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691176</t>
+          <t>693371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161628</t>
+          <t>160910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205310</t>
+          <t>206461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>191620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229244</t>
+          <t>229542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>364525</t>
+          <t>365656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>425124</t>
+          <t>422258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328491</t>
+          <t>327340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>372173</t>
+          <t>372891</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311621</t>
+          <t>311323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348823</t>
+          <t>349245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649542</t>
+          <t>652408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>710141</t>
+          <t>709010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95096</t>
+          <t>100626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>323526</t>
+          <t>322173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>245772</t>
+          <t>244727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>345735</t>
+          <t>333416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>291810</t>
+          <t>298139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>608949</t>
+          <t>609683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>563211</t>
+          <t>564564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>791641</t>
+          <t>786111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366387</t>
+          <t>378706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466350</t>
+          <t>467395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>989909</t>
+          <t>989175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1307048</t>
+          <t>1300719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>197413</t>
+          <t>199171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239759</t>
+          <t>242109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187822</t>
+          <t>187947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219924</t>
+          <t>221463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>398190</t>
+          <t>398135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453188</t>
+          <t>451987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319525</t>
+          <t>317175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361871</t>
+          <t>360113</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>323577</t>
+          <t>322038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>355679</t>
+          <t>355554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>649597</t>
+          <t>650798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>704595</t>
+          <t>704650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100541</t>
+          <t>101483</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129189</t>
+          <t>128660</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62261</t>
+          <t>62408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>232613</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116003</t>
+          <t>137713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339863</t>
+          <t>341296</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238112</t>
+          <t>238641</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266760</t>
+          <t>265818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>376687</t>
+          <t>375176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>545528</t>
+          <t>545381</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>635227</t>
+          <t>633794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>859087</t>
+          <t>837377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105144</t>
+          <t>102707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129984</t>
+          <t>130557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>254579</t>
+          <t>253047</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>280761</t>
+          <t>281931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>364597</t>
+          <t>364324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>404499</t>
+          <t>404749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,38%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151091</t>
+          <t>150518</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175931</t>
+          <t>178368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>143508</t>
+          <t>142338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>169690</t>
+          <t>171222</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>300844</t>
+          <t>300594</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>340746</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>804984</t>
+          <t>822048</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1168999</t>
+          <t>1173211</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1129133</t>
+          <t>1124899</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1500600</t>
+          <t>1504516</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2136716</t>
+          <t>2135725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2634551</t>
+          <t>2627855</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2281547</t>
+          <t>2277335</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2645562</t>
+          <t>2628498</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2152648</t>
+          <t>2148732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2524115</t>
+          <t>2528349</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4469243</t>
+          <t>4475939</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4967078</t>
+          <t>4968069</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104374</t>
+          <t>104558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142640</t>
+          <t>145717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>175419</t>
+          <t>176288</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>215828</t>
+          <t>216673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>289971</t>
+          <t>290270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>349226</t>
+          <t>345303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345079</t>
+          <t>342002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383345</t>
+          <t>383161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242231</t>
+          <t>241386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282640</t>
+          <t>281771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>596552</t>
+          <t>600475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655807</t>
+          <t>655508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235396</t>
+          <t>236511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>287438</t>
+          <t>289795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>251204</t>
+          <t>251009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302986</t>
+          <t>301035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>500842</t>
+          <t>502809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>574341</t>
+          <t>579325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433121</t>
+          <t>430764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485163</t>
+          <t>484048</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312316</t>
+          <t>314267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364098</t>
+          <t>364293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>761519</t>
+          <t>756535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>835018</t>
+          <t>833051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>256920</t>
+          <t>255190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304952</t>
+          <t>304731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>277355</t>
+          <t>272959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>327870</t>
+          <t>326425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>546626</t>
+          <t>548222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>617582</t>
+          <t>620589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326686</t>
+          <t>326907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>374718</t>
+          <t>376448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>347072</t>
+          <t>348517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>397587</t>
+          <t>401983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>688998</t>
+          <t>685991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>759954</t>
+          <t>758358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231883</t>
+          <t>229850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>279050</t>
+          <t>277072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200735</t>
+          <t>198427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243793</t>
+          <t>244090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>444107</t>
+          <t>443467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>507711</t>
+          <t>508727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235652</t>
+          <t>237630</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282819</t>
+          <t>284852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260291</t>
+          <t>259994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303349</t>
+          <t>305657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>511075</t>
+          <t>510059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574679</t>
+          <t>575319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174223</t>
+          <t>171140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>210998</t>
+          <t>210719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155465</t>
+          <t>154701</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195403</t>
+          <t>194667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340476</t>
+          <t>339329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>395044</t>
+          <t>394878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167990</t>
+          <t>168269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204765</t>
+          <t>207848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204399</t>
+          <t>205135</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>244337</t>
+          <t>245101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383746</t>
+          <t>383912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>438314</t>
+          <t>439461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96667</t>
+          <t>96286</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129064</t>
+          <t>128228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>144812</t>
+          <t>146458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179080</t>
+          <t>179141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>251636</t>
+          <t>252618</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>300880</t>
+          <t>297903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160046</t>
+          <t>160882</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192443</t>
+          <t>192824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159468</t>
+          <t>159407</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193736</t>
+          <t>192090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>326778</t>
+          <t>329755</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>376022</t>
+          <t>375040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87389</t>
+          <t>88526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117449</t>
+          <t>116750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>181195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>217114</t>
+          <t>219500</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>278446</t>
+          <t>280829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>326995</t>
+          <t>328599</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91400</t>
+          <t>92099</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121460</t>
+          <t>120323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110908</t>
+          <t>108522</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147345</t>
+          <t>146827</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209875</t>
+          <t>208271</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258424</t>
+          <t>256041</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1269057</t>
+          <t>1266243</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1384498</t>
+          <t>1378935</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1475908</t>
+          <t>1472231</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1591174</t>
+          <t>1591192</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2775725</t>
+          <t>2778487</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2940722</t>
+          <t>2944256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1847065</t>
+          <t>1852628</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1962506</t>
+          <t>1965320</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1727585</t>
+          <t>1727567</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1842851</t>
+          <t>1846528</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3609600</t>
+          <t>3606066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3774597</t>
+          <t>3771835</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>57354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88068</t>
+          <t>88923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106636</t>
+          <t>108567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144979</t>
+          <t>147256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>172624</t>
+          <t>173475</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221343</t>
+          <t>223138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>366078</t>
+          <t>365223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398275</t>
+          <t>396792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285251</t>
+          <t>282974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>323594</t>
+          <t>321663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>663033</t>
+          <t>661238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711752</t>
+          <t>710901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112038</t>
+          <t>113589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153984</t>
+          <t>153976</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147524</t>
+          <t>149369</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192243</t>
+          <t>194601</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276314</t>
+          <t>273818</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>333950</t>
+          <t>335978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>531345</t>
+          <t>531353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>573291</t>
+          <t>571740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>418012</t>
+          <t>415654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462731</t>
+          <t>460886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>961635</t>
+          <t>959607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019271</t>
+          <t>1021767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150448</t>
+          <t>149848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198667</t>
+          <t>195200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176983</t>
+          <t>179428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225796</t>
+          <t>228587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>337343</t>
+          <t>338120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>408844</t>
+          <t>404442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483196</t>
+          <t>486663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531415</t>
+          <t>532015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>485054</t>
+          <t>482263</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>533867</t>
+          <t>531422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>983868</t>
+          <t>988270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1055369</t>
+          <t>1054592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130938</t>
+          <t>132033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177044</t>
+          <t>179419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151874</t>
+          <t>153004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197279</t>
+          <t>201277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>296386</t>
+          <t>294134</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>363355</t>
+          <t>361497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>437573</t>
+          <t>435198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>483679</t>
+          <t>482584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>418920</t>
+          <t>414922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464325</t>
+          <t>463195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>867461</t>
+          <t>869319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>934430</t>
+          <t>936682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>89070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125968</t>
+          <t>125851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98465</t>
+          <t>95028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135731</t>
+          <t>132927</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193762</t>
+          <t>196422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>250206</t>
+          <t>251220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>303461</t>
+          <t>303578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339401</t>
+          <t>340359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>312069</t>
+          <t>314873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349335</t>
+          <t>352772</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>627023</t>
+          <t>626009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>683467</t>
+          <t>680807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51808</t>
+          <t>52816</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82841</t>
+          <t>82793</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>98961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>135976</t>
+          <t>135407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>159588</t>
+          <t>159749</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206415</t>
+          <t>207135</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226945</t>
+          <t>226993</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257978</t>
+          <t>256970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218020</t>
+          <t>218589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254119</t>
+          <t>255035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>457367</t>
+          <t>456647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504194</t>
+          <t>504033</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55556</t>
+          <t>55173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85498</t>
+          <t>84294</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>179785</t>
+          <t>178367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>219319</t>
+          <t>220764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241238</t>
+          <t>237989</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291456</t>
+          <t>292215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164353</t>
+          <t>165557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194295</t>
+          <t>194678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168562</t>
+          <t>167117</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208096</t>
+          <t>209514</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>346276</t>
+          <t>345517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>396494</t>
+          <t>399743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>719512</t>
+          <t>719529</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>820113</t>
+          <t>818528</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1045472</t>
+          <t>1041111</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1157918</t>
+          <t>1153592</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1793702</t>
+          <t>1797037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1945254</t>
+          <t>1943348</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2604908</t>
+          <t>2606493</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2705509</t>
+          <t>2705492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2399293</t>
+          <t>2403619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2511739</t>
+          <t>2516100</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5036978</t>
+          <t>5038884</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5188530</t>
+          <t>5185195</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63806</t>
+          <t>64306</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97520</t>
+          <t>96577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>133075</t>
+          <t>131769</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170393</t>
+          <t>170275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205114</t>
+          <t>204902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256251</t>
+          <t>258609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321943</t>
+          <t>322886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355657</t>
+          <t>355157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225362</t>
+          <t>225480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262680</t>
+          <t>263986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558967</t>
+          <t>556609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>610104</t>
+          <t>610316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136968</t>
+          <t>136737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180016</t>
+          <t>181181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186083</t>
+          <t>187161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231965</t>
+          <t>230280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>335782</t>
+          <t>333004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>398049</t>
+          <t>396289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410480</t>
+          <t>409315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>453528</t>
+          <t>453759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331579</t>
+          <t>333264</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377461</t>
+          <t>376383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>755991</t>
+          <t>757751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818258</t>
+          <t>821036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>208563</t>
+          <t>208038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>260756</t>
+          <t>259865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204566</t>
+          <t>206968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253480</t>
+          <t>254050</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>429865</t>
+          <t>430202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>499539</t>
+          <t>497248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>408341</t>
+          <t>409232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>460534</t>
+          <t>461059</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>407906</t>
+          <t>407336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456820</t>
+          <t>454418</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>830944</t>
+          <t>833235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>900618</t>
+          <t>900281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222356</t>
+          <t>221197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273021</t>
+          <t>273260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>221032</t>
+          <t>222596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>271466</t>
+          <t>273747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>459016</t>
+          <t>459397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>530703</t>
+          <t>530861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>373027</t>
+          <t>372788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>423692</t>
+          <t>424851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377611</t>
+          <t>375330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>428045</t>
+          <t>426481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>764422</t>
+          <t>764264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>836109</t>
+          <t>835728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>150050</t>
+          <t>146282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193581</t>
+          <t>193090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204399</t>
+          <t>206266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252073</t>
+          <t>252640</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>369256</t>
+          <t>366502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>433293</t>
+          <t>432269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>284337</t>
+          <t>284828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>327868</t>
+          <t>331636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244776</t>
+          <t>244209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292450</t>
+          <t>290583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>541474</t>
+          <t>542498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>605511</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110713</t>
+          <t>108360</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146706</t>
+          <t>145335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>153400</t>
+          <t>155257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194620</t>
+          <t>192777</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>271902</t>
+          <t>274740</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>327241</t>
+          <t>325430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187624</t>
+          <t>188995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223617</t>
+          <t>225970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183142</t>
+          <t>184985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>224362</t>
+          <t>222505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384851</t>
+          <t>386662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>440190</t>
+          <t>437352</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118885</t>
+          <t>116907</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>145032</t>
+          <t>146271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252222</t>
+          <t>250902</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>293516</t>
+          <t>294036</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>378262</t>
+          <t>379521</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431568</t>
+          <t>431269</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111966</t>
+          <t>110727</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138113</t>
+          <t>140091</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106653</t>
+          <t>106133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147947</t>
+          <t>149267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225599</t>
+          <t>225898</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278905</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1093989</t>
+          <t>1092772</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1211924</t>
+          <t>1209112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1455725</t>
+          <t>1458520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1574322</t>
+          <t>1578005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2579108</t>
+          <t>2589110</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2745765</t>
+          <t>2748514</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2182426</t>
+          <t>2185238</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2300361</t>
+          <t>2301578</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1970220</t>
+          <t>1966537</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2088817</t>
+          <t>2086022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4193127</t>
+          <t>4190378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4359784</t>
+          <t>4349782</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>57763</t>
+          <t>56599</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36325</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89716</t>
+          <t>85072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>115072</t>
+          <t>132379</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94030</t>
+          <t>107227</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140381</t>
+          <t>158151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>172835</t>
+          <t>188979</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140568</t>
+          <t>154008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209794</t>
+          <t>228649</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>342224</t>
+          <t>351194</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310271</t>
+          <t>322721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>363662</t>
+          <t>369351</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>198128</t>
+          <t>230133</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172819</t>
+          <t>204361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219170</t>
+          <t>255285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>540352</t>
+          <t>581326</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503393</t>
+          <t>541656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572619</t>
+          <t>616297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>149562</t>
+          <t>158817</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126601</t>
+          <t>135399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174915</t>
+          <t>186538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>165802</t>
+          <t>190628</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98893</t>
+          <t>169681</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>198489</t>
+          <t>214146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>315363</t>
+          <t>349446</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>240494</t>
+          <t>314417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355830</t>
+          <t>383665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>272799</t>
+          <t>316768</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247446</t>
+          <t>289047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>295760</t>
+          <t>340186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>345702</t>
+          <t>310455</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313015</t>
+          <t>286937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>412611</t>
+          <t>331402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>618502</t>
+          <t>627223</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>578035</t>
+          <t>593004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>693371</t>
+          <t>662252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422361</t>
+          <t>475585</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422361</t>
+          <t>475585</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422361</t>
+          <t>475585</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>933865</t>
+          <t>976669</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>933865</t>
+          <t>976669</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>933865</t>
+          <t>976669</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>183535</t>
+          <t>219323</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160910</t>
+          <t>193875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206461</t>
+          <t>246435</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>210475</t>
+          <t>245717</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191620</t>
+          <t>226492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229542</t>
+          <t>266442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>394010</t>
+          <t>465039</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>365656</t>
+          <t>430118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>422258</t>
+          <t>496516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>350266</t>
+          <t>398950</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327340</t>
+          <t>371838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>372891</t>
+          <t>424398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>330390</t>
+          <t>374151</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311323</t>
+          <t>353426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>349245</t>
+          <t>393376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>680656</t>
+          <t>773101</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652408</t>
+          <t>741624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>709010</t>
+          <t>808022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533801</t>
+          <t>618273</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533801</t>
+          <t>618273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533801</t>
+          <t>618273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>540865</t>
+          <t>619868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540865</t>
+          <t>619868</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>540865</t>
+          <t>619868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1074666</t>
+          <t>1238140</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1074666</t>
+          <t>1238140</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1074666</t>
+          <t>1238140</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>224352</t>
+          <t>248916</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100626</t>
+          <t>223554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>322173</t>
+          <t>275149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>274506</t>
+          <t>258316</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244727</t>
+          <t>239367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>333416</t>
+          <t>280487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>498858</t>
+          <t>507232</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>298139</t>
+          <t>473234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>609683</t>
+          <t>540292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>662385</t>
+          <t>450572</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>564564</t>
+          <t>424339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>786111</t>
+          <t>475934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>437616</t>
+          <t>477791</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378706</t>
+          <t>455620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>467395</t>
+          <t>496740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1100000</t>
+          <t>928364</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>989175</t>
+          <t>895304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1300719</t>
+          <t>962362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886737</t>
+          <t>699488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886737</t>
+          <t>699488</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886737</t>
+          <t>699488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712122</t>
+          <t>736107</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712122</t>
+          <t>736107</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712122</t>
+          <t>736107</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598858</t>
+          <t>1435596</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598858</t>
+          <t>1435596</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598858</t>
+          <t>1435596</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>219753</t>
+          <t>239947</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199171</t>
+          <t>217145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242109</t>
+          <t>264522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>204671</t>
+          <t>226651</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187947</t>
+          <t>208279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>245861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>424424</t>
+          <t>466598</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>398135</t>
+          <t>436727</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>451987</t>
+          <t>496128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>339531</t>
+          <t>367506</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>317175</t>
+          <t>342931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360113</t>
+          <t>390308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>338830</t>
+          <t>378643</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>322038</t>
+          <t>359433</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>355554</t>
+          <t>397015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>678361</t>
+          <t>746149</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>650798</t>
+          <t>716619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>704650</t>
+          <t>776020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559284</t>
+          <t>607453</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559284</t>
+          <t>607453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559284</t>
+          <t>607453</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543501</t>
+          <t>605294</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>543501</t>
+          <t>605294</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>543501</t>
+          <t>605294</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1102785</t>
+          <t>1212747</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1102785</t>
+          <t>1212747</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102785</t>
+          <t>1212747</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>114569</t>
+          <t>127471</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101483</t>
+          <t>112764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>128660</t>
+          <t>143339</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>148857</t>
+          <t>163446</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62408</t>
+          <t>148479</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>232613</t>
+          <t>179247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>263426</t>
+          <t>290918</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137713</t>
+          <t>266413</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341296</t>
+          <t>310049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>252732</t>
+          <t>278556</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238641</t>
+          <t>262688</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265818</t>
+          <t>293263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>458932</t>
+          <t>275122</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>375176</t>
+          <t>259321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>545381</t>
+          <t>290089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>711664</t>
+          <t>553677</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>633794</t>
+          <t>534546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>837377</t>
+          <t>578182</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367301</t>
+          <t>406027</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367301</t>
+          <t>406027</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367301</t>
+          <t>406027</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438568</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438568</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438568</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975090</t>
+          <t>844595</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975090</t>
+          <t>844595</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975090</t>
+          <t>844595</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>116568</t>
+          <t>127230</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102707</t>
+          <t>112558</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130557</t>
+          <t>141273</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>267629</t>
+          <t>291693</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>253047</t>
+          <t>277790</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>281931</t>
+          <t>308102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>384196</t>
+          <t>418924</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>364324</t>
+          <t>398171</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>404749</t>
+          <t>441985</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,34%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>164507</t>
+          <t>180944</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>150518</t>
+          <t>166901</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178368</t>
+          <t>195616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>156640</t>
+          <t>170907</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142338</t>
+          <t>154498</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>171222</t>
+          <t>184810</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>321147</t>
+          <t>351850</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>300594</t>
+          <t>328789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>341019</t>
+          <t>372603</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>308174</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>308174</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>308174</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424269</t>
+          <t>462600</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424269</t>
+          <t>462600</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424269</t>
+          <t>462600</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705343</t>
+          <t>770774</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705343</t>
+          <t>770774</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705343</t>
+          <t>770774</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1066102</t>
+          <t>1178305</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>822048</t>
+          <t>1117217</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1173211</t>
+          <t>1240274</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1387012</t>
+          <t>1508830</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1124899</t>
+          <t>1458472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1504516</t>
+          <t>1558289</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2453114</t>
+          <t>2687135</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2135725</t>
+          <t>2610556</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2627855</t>
+          <t>2762835</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2384444</t>
+          <t>2344489</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2277335</t>
+          <t>2282520</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2628498</t>
+          <t>2405577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2266236</t>
+          <t>2217201</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2148732</t>
+          <t>2167742</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2528349</t>
+          <t>2267559</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4650680</t>
+          <t>4561690</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4475939</t>
+          <t>4485990</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4968069</t>
+          <t>4638269</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
